--- a/tame_output/ON/bt/strategyON_20231205.xlsx
+++ b/tame_output/ON/bt/strategyON_20231205.xlsx
@@ -906,7 +906,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-14.2%</t>
+          <t>-14.1%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
     </row>
@@ -41990,7 +41990,7 @@
         <v>45222</v>
       </c>
       <c r="B1760" t="n">
-        <v>3.048806209055149</v>
+        <v>3.04880620905515</v>
       </c>
       <c r="C1760" t="n">
         <v>2.992474709334104</v>
@@ -42197,7 +42197,7 @@
         <v>45231</v>
       </c>
       <c r="B1769" t="n">
-        <v>3.093259956227613</v>
+        <v>3.093259956227614</v>
       </c>
       <c r="C1769" t="n">
         <v>3.049962823512704</v>
@@ -42243,7 +42243,7 @@
         <v>45233</v>
       </c>
       <c r="B1771" t="n">
-        <v>3.069025022408316</v>
+        <v>3.069025022408317</v>
       </c>
       <c r="C1771" t="n">
         <v>3.051179068073428</v>
@@ -42266,7 +42266,7 @@
         <v>45234</v>
       </c>
       <c r="B1772" t="n">
-        <v>3.085392865708494</v>
+        <v>3.085392865708495</v>
       </c>
       <c r="C1772" t="n">
         <v>3.056704057212575</v>
@@ -42289,7 +42289,7 @@
         <v>45235</v>
       </c>
       <c r="B1773" t="n">
-        <v>3.073923642968023</v>
+        <v>3.073923642968024</v>
       </c>
       <c r="C1773" t="n">
         <v>3.057781629850306</v>
@@ -42312,7 +42312,7 @@
         <v>45236</v>
       </c>
       <c r="B1774" t="n">
-        <v>3.074518669066012</v>
+        <v>3.074518669066013</v>
       </c>
       <c r="C1774" t="n">
         <v>3.058531492021579</v>
@@ -42335,7 +42335,7 @@
         <v>45237</v>
       </c>
       <c r="B1775" t="n">
-        <v>3.087505451293021</v>
+        <v>3.087505451293022</v>
       </c>
       <c r="C1775" t="n">
         <v>3.05676708948516</v>
@@ -42358,7 +42358,7 @@
         <v>45238</v>
       </c>
       <c r="B1776" t="n">
-        <v>3.125945945239774</v>
+        <v>3.125945945239775</v>
       </c>
       <c r="C1776" t="n">
         <v>3.060334699322022</v>
@@ -42404,7 +42404,7 @@
         <v>45240</v>
       </c>
       <c r="B1778" t="n">
-        <v>3.135555340167861</v>
+        <v>3.135555340167862</v>
       </c>
       <c r="C1778" t="n">
         <v>3.081785372698861</v>
@@ -42427,7 +42427,7 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.134141625216942</v>
+        <v>3.134141625216943</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
@@ -42450,7 +42450,7 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.132018996454038</v>
+        <v>3.132018996454039</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780867</v>
+        <v>3.120443325780868</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42496,7 +42496,7 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.09520660653793</v>
+        <v>3.095206606537931</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
@@ -42519,7 +42519,7 @@
         <v>45245</v>
       </c>
       <c r="B1783" t="n">
-        <v>3.147410092597766</v>
+        <v>3.147410092597767</v>
       </c>
       <c r="C1783" t="n">
         <v>3.0856881010767</v>
@@ -42542,7 +42542,7 @@
         <v>45246</v>
       </c>
       <c r="B1784" t="n">
-        <v>3.120684616527685</v>
+        <v>3.120684616527686</v>
       </c>
       <c r="C1784" t="n">
         <v>3.089704189836242</v>
@@ -42565,7 +42565,7 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844644</v>
+        <v>3.118866618844645</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502547</v>
+        <v>3.141819250502548</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.14673011872803</v>
+        <v>3.146730118728031</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42657,7 +42657,7 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702054</v>
+        <v>3.120735995702055</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.14605337248781</v>
+        <v>3.146053372487811</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42703,7 +42703,7 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.14626574482338</v>
+        <v>3.146265744823381</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524821</v>
+        <v>3.157777201524822</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068701</v>
+        <v>3.157294380068702</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714842</v>
+        <v>3.147014107714843</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42795,7 +42795,7 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.136752015083875</v>
+        <v>3.136752015083876</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
@@ -42818,7 +42818,7 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666732</v>
+        <v>3.162269743666733</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097097</v>
+        <v>3.163432091097098</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.185514355963478</v>
+        <v>3.185514355963479</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
@@ -42933,7 +42933,7 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742722</v>
+        <v>3.238767863742723</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
@@ -42956,22 +42956,22 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>2.895436922045264</v>
+        <v>2.895436922045265</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
       </c>
       <c r="D1802" t="n">
-        <v>1.282525985066862</v>
+        <v>1.283199566847909</v>
       </c>
       <c r="E1802" t="n">
-        <v>3.604638731911853</v>
+        <v>3.604908164624272</v>
       </c>
       <c r="F1802" t="n">
-        <v>1.444662544796309</v>
+        <v>1.444258359719086</v>
       </c>
       <c r="G1802" t="n">
-        <v>3.958782289076642</v>
+        <v>3.958539778030308</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231205.xlsx
+++ b/tame_output/ON/bt/strategyON_20231205.xlsx
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-14.1%</t>
+          <t>-13.9%</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-64.8%</t>
+          <t>-64.7%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>105.5%</t>
+          <t>105.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-15.1%</t>
         </is>
       </c>
     </row>
@@ -41921,7 +41921,7 @@
         <v>45219</v>
       </c>
       <c r="B1757" t="n">
-        <v>2.902669647939157</v>
+        <v>2.902669647939156</v>
       </c>
       <c r="C1757" t="n">
         <v>2.968547780644436</v>
@@ -41944,7 +41944,7 @@
         <v>45220</v>
       </c>
       <c r="B1758" t="n">
-        <v>2.912903254947841</v>
+        <v>2.91290325494784</v>
       </c>
       <c r="C1758" t="n">
         <v>2.965146865274802</v>
@@ -42174,7 +42174,7 @@
         <v>45230</v>
       </c>
       <c r="B1768" t="n">
-        <v>3.059751997255681</v>
+        <v>3.05975199725568</v>
       </c>
       <c r="C1768" t="n">
         <v>3.034928653249013</v>
@@ -42197,7 +42197,7 @@
         <v>45231</v>
       </c>
       <c r="B1769" t="n">
-        <v>3.093259956227614</v>
+        <v>3.093259956227613</v>
       </c>
       <c r="C1769" t="n">
         <v>3.049962823512704</v>
@@ -42243,7 +42243,7 @@
         <v>45233</v>
       </c>
       <c r="B1771" t="n">
-        <v>3.069025022408317</v>
+        <v>3.069025022408316</v>
       </c>
       <c r="C1771" t="n">
         <v>3.051179068073428</v>
@@ -42266,7 +42266,7 @@
         <v>45234</v>
       </c>
       <c r="B1772" t="n">
-        <v>3.085392865708495</v>
+        <v>3.085392865708494</v>
       </c>
       <c r="C1772" t="n">
         <v>3.056704057212575</v>
@@ -42289,7 +42289,7 @@
         <v>45235</v>
       </c>
       <c r="B1773" t="n">
-        <v>3.073923642968024</v>
+        <v>3.073923642968023</v>
       </c>
       <c r="C1773" t="n">
         <v>3.057781629850306</v>
@@ -42312,7 +42312,7 @@
         <v>45236</v>
       </c>
       <c r="B1774" t="n">
-        <v>3.074518669066013</v>
+        <v>3.074518669066012</v>
       </c>
       <c r="C1774" t="n">
         <v>3.058531492021579</v>
@@ -42335,7 +42335,7 @@
         <v>45237</v>
       </c>
       <c r="B1775" t="n">
-        <v>3.087505451293022</v>
+        <v>3.087505451293021</v>
       </c>
       <c r="C1775" t="n">
         <v>3.05676708948516</v>
@@ -42358,7 +42358,7 @@
         <v>45238</v>
       </c>
       <c r="B1776" t="n">
-        <v>3.125945945239775</v>
+        <v>3.125945945239774</v>
       </c>
       <c r="C1776" t="n">
         <v>3.060334699322022</v>
@@ -42404,7 +42404,7 @@
         <v>45240</v>
       </c>
       <c r="B1778" t="n">
-        <v>3.135555340167862</v>
+        <v>3.135555340167861</v>
       </c>
       <c r="C1778" t="n">
         <v>3.081785372698861</v>
@@ -42427,7 +42427,7 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.134141625216943</v>
+        <v>3.134141625216942</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
@@ -42450,7 +42450,7 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.132018996454039</v>
+        <v>3.132018996454038</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780868</v>
+        <v>3.120443325780867</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42496,7 +42496,7 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.095206606537931</v>
+        <v>3.09520660653793</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
@@ -42519,7 +42519,7 @@
         <v>45245</v>
       </c>
       <c r="B1783" t="n">
-        <v>3.147410092597767</v>
+        <v>3.147410092597766</v>
       </c>
       <c r="C1783" t="n">
         <v>3.0856881010767</v>
@@ -42542,7 +42542,7 @@
         <v>45246</v>
       </c>
       <c r="B1784" t="n">
-        <v>3.120684616527686</v>
+        <v>3.120684616527685</v>
       </c>
       <c r="C1784" t="n">
         <v>3.089704189836242</v>
@@ -42565,7 +42565,7 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844645</v>
+        <v>3.118866618844644</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502548</v>
+        <v>3.141819250502547</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.146730118728031</v>
+        <v>3.14673011872803</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42657,7 +42657,7 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702055</v>
+        <v>3.120735995702054</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.146053372487811</v>
+        <v>3.14605337248781</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42703,7 +42703,7 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.146265744823381</v>
+        <v>3.14626574482338</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524822</v>
+        <v>3.157777201524821</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068702</v>
+        <v>3.157294380068701</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714843</v>
+        <v>3.147014107714842</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42795,7 +42795,7 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.136752015083876</v>
+        <v>3.136752015083875</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
@@ -42818,7 +42818,7 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666733</v>
+        <v>3.162269743666732</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097098</v>
+        <v>3.163432091097097</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.185514355963479</v>
+        <v>3.185514355963478</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
@@ -42956,22 +42956,22 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>2.895436922045265</v>
+        <v>2.895436922045264</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
       </c>
       <c r="D1802" t="n">
-        <v>1.283199566847909</v>
+        <v>1.284679268937456</v>
       </c>
       <c r="E1802" t="n">
-        <v>3.604908164624272</v>
+        <v>3.605500045460091</v>
       </c>
       <c r="F1802" t="n">
-        <v>1.444258359719086</v>
+        <v>1.446034519686212</v>
       </c>
       <c r="G1802" t="n">
-        <v>3.958539778030308</v>
+        <v>3.959605474010583</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231205.xlsx
+++ b/tame_output/ON/bt/strategyON_20231205.xlsx
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -934,17 +934,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>84.9%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-107.0%</t>
+          <t>-149.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-10.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,32 +992,32 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.4%</t>
+          <t>454.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-13.2%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-13.9%</t>
+          <t>-55.7%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-48.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>86.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>1.4%</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-85.8%</t>
+          <t>-113.9%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-10.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1298,17 +1298,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-64.7%</t>
+          <t>-92.5%</t>
         </is>
       </c>
     </row>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>101.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1393,17 +1393,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-40.0%</t>
+          <t>-56.9%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>105.6%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.3%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-31.8%</t>
         </is>
       </c>
     </row>
@@ -41789,16 +41789,16 @@
         <v>2.950191610492619</v>
       </c>
       <c r="D1751" t="n">
-        <v>0.5263819502712856</v>
+        <v>0.1033322769875972</v>
       </c>
       <c r="E1751" t="n">
-        <v>3.160387966287387</v>
+        <v>2.991168096973911</v>
       </c>
       <c r="F1751" t="n">
-        <v>1.317017491302278</v>
+        <v>1.035794635427876</v>
       </c>
       <c r="G1751" t="n">
-        <v>3.740402105273988</v>
+        <v>3.571668391749347</v>
       </c>
     </row>
     <row r="1752">
@@ -41812,16 +41812,16 @@
         <v>2.953840430523644</v>
       </c>
       <c r="D1752" t="n">
-        <v>0.526008537260285</v>
+        <v>0.1029588639765965</v>
       </c>
       <c r="E1752" t="n">
-        <v>3.163887421114011</v>
+        <v>2.994667551800536</v>
       </c>
       <c r="F1752" t="n">
-        <v>1.317017491302278</v>
+        <v>1.035794635427876</v>
       </c>
       <c r="G1752" t="n">
-        <v>3.744050925305012</v>
+        <v>3.575317211780372</v>
       </c>
     </row>
     <row r="1753">
@@ -41835,16 +41835,16 @@
         <v>2.959094075792072</v>
       </c>
       <c r="D1753" t="n">
-        <v>0.5315194817269985</v>
+        <v>0.1084698084433101</v>
       </c>
       <c r="E1753" t="n">
-        <v>3.171345444169124</v>
+        <v>3.002125574855649</v>
       </c>
       <c r="F1753" t="n">
-        <v>1.317017491302278</v>
+        <v>1.035794635427876</v>
       </c>
       <c r="G1753" t="n">
-        <v>3.74930457057344</v>
+        <v>3.580570857048799</v>
       </c>
     </row>
     <row r="1754">
@@ -41858,16 +41858,16 @@
         <v>2.957874679524909</v>
       </c>
       <c r="D1754" t="n">
-        <v>0.5317900590683243</v>
+        <v>0.1087403857846359</v>
       </c>
       <c r="E1754" t="n">
-        <v>3.170234278838492</v>
+        <v>3.001014409525016</v>
       </c>
       <c r="F1754" t="n">
-        <v>1.317514017604929</v>
+        <v>1.036291161730527</v>
       </c>
       <c r="G1754" t="n">
-        <v>3.748383090087867</v>
+        <v>3.579649376563227</v>
       </c>
     </row>
     <row r="1755">
@@ -41881,16 +41881,16 @@
         <v>2.95420083304114</v>
       </c>
       <c r="D1755" t="n">
-        <v>0.5397752274500688</v>
+        <v>0.1167255541663804</v>
       </c>
       <c r="E1755" t="n">
-        <v>3.169754499707421</v>
+        <v>3.000534630393946</v>
       </c>
       <c r="F1755" t="n">
-        <v>1.319741563641705</v>
+        <v>1.038518707767304</v>
       </c>
       <c r="G1755" t="n">
-        <v>3.746045771226165</v>
+        <v>3.577312057701524</v>
       </c>
     </row>
     <row r="1756">
@@ -41904,16 +41904,16 @@
         <v>2.969006534107256</v>
       </c>
       <c r="D1756" t="n">
-        <v>0.5288888636790251</v>
+        <v>0.1058391903953367</v>
       </c>
       <c r="E1756" t="n">
-        <v>3.180205655265119</v>
+        <v>3.010985785951644</v>
       </c>
       <c r="F1756" t="n">
-        <v>1.319741563641705</v>
+        <v>1.038518707767304</v>
       </c>
       <c r="G1756" t="n">
-        <v>3.760851472292281</v>
+        <v>3.59211775876764</v>
       </c>
     </row>
     <row r="1757">
@@ -41927,16 +41927,16 @@
         <v>2.968547780644436</v>
       </c>
       <c r="D1757" t="n">
-        <v>0.5370060036366703</v>
+        <v>0.1139563303529819</v>
       </c>
       <c r="E1757" t="n">
-        <v>3.182993757785357</v>
+        <v>3.013773888471882</v>
       </c>
       <c r="F1757" t="n">
-        <v>1.319741563641705</v>
+        <v>1.038518707767304</v>
       </c>
       <c r="G1757" t="n">
-        <v>3.760392718829461</v>
+        <v>3.591659005304821</v>
       </c>
     </row>
     <row r="1758">
@@ -41950,16 +41950,16 @@
         <v>2.965146865274802</v>
       </c>
       <c r="D1758" t="n">
-        <v>0.5415153518624555</v>
+        <v>0.1184656785787671</v>
       </c>
       <c r="E1758" t="n">
-        <v>3.181396581706038</v>
+        <v>3.012176712392562</v>
       </c>
       <c r="F1758" t="n">
-        <v>1.319741563641705</v>
+        <v>1.038518707767304</v>
       </c>
       <c r="G1758" t="n">
-        <v>3.756991803459827</v>
+        <v>3.588258089935187</v>
       </c>
     </row>
     <row r="1759">
@@ -41973,16 +41973,16 @@
         <v>2.964689051375926</v>
       </c>
       <c r="D1759" t="n">
-        <v>0.5312082262050204</v>
+        <v>0.1081585529213319</v>
       </c>
       <c r="E1759" t="n">
-        <v>3.176815917544187</v>
+        <v>3.007596048230712</v>
       </c>
       <c r="F1759" t="n">
-        <v>1.312743181326852</v>
+        <v>1.031520325452451</v>
       </c>
       <c r="G1759" t="n">
-        <v>3.752334960172039</v>
+        <v>3.583601246647398</v>
       </c>
     </row>
     <row r="1760">
@@ -41996,16 +41996,16 @@
         <v>2.992474709334104</v>
       </c>
       <c r="D1760" t="n">
-        <v>0.4829655773193084</v>
+        <v>0.05991590403561992</v>
       </c>
       <c r="E1760" t="n">
-        <v>3.185304515948081</v>
+        <v>3.016084646634605</v>
       </c>
       <c r="F1760" t="n">
-        <v>1.312743181326852</v>
+        <v>1.031520325452451</v>
       </c>
       <c r="G1760" t="n">
-        <v>3.780120618130216</v>
+        <v>3.611386904605576</v>
       </c>
     </row>
     <row r="1761">
@@ -42019,16 +42019,16 @@
         <v>3.010249418375564</v>
       </c>
       <c r="D1761" t="n">
-        <v>0.4900635782868101</v>
+        <v>0.0670139050031216</v>
       </c>
       <c r="E1761" t="n">
-        <v>3.205918425376541</v>
+        <v>3.036698556063066</v>
       </c>
       <c r="F1761" t="n">
-        <v>1.312850379438228</v>
+        <v>1.031627523563826</v>
       </c>
       <c r="G1761" t="n">
-        <v>3.797959646038502</v>
+        <v>3.629225932513862</v>
       </c>
     </row>
     <row r="1762">
@@ -42042,16 +42042,16 @@
         <v>3.010722978056604</v>
       </c>
       <c r="D1762" t="n">
-        <v>0.4912666445829165</v>
+        <v>0.06821697129922799</v>
       </c>
       <c r="E1762" t="n">
-        <v>3.206873211576024</v>
+        <v>3.037653342262549</v>
       </c>
       <c r="F1762" t="n">
-        <v>1.312850379438228</v>
+        <v>1.031627523563826</v>
       </c>
       <c r="G1762" t="n">
-        <v>3.798433205719543</v>
+        <v>3.629699492194902</v>
       </c>
     </row>
     <row r="1763">
@@ -42065,16 +42065,16 @@
         <v>3.016062350193502</v>
       </c>
       <c r="D1763" t="n">
-        <v>0.493619691916162</v>
+        <v>0.07057001863247347</v>
       </c>
       <c r="E1763" t="n">
-        <v>3.213153802646219</v>
+        <v>3.043933933332744</v>
       </c>
       <c r="F1763" t="n">
-        <v>1.315203426771473</v>
+        <v>1.033980570897072</v>
       </c>
       <c r="G1763" t="n">
-        <v>3.805184406256387</v>
+        <v>3.636450692731747</v>
       </c>
     </row>
     <row r="1764">
@@ -42088,16 +42088,16 @@
         <v>3.030639375029551</v>
       </c>
       <c r="D1764" t="n">
-        <v>0.4947359739073881</v>
+        <v>0.07168630062369963</v>
       </c>
       <c r="E1764" t="n">
-        <v>3.22817734027876</v>
+        <v>3.058957470965284</v>
       </c>
       <c r="F1764" t="n">
-        <v>1.316319708762699</v>
+        <v>1.035096852888298</v>
       </c>
       <c r="G1764" t="n">
-        <v>3.820431200287172</v>
+        <v>3.651697486762532</v>
       </c>
     </row>
     <row r="1765">
@@ -42111,16 +42111,16 @@
         <v>3.030564355893199</v>
       </c>
       <c r="D1765" t="n">
-        <v>0.4984739299684435</v>
+        <v>0.07542425668475505</v>
       </c>
       <c r="E1765" t="n">
-        <v>3.229597503566829</v>
+        <v>3.060377634253354</v>
       </c>
       <c r="F1765" t="n">
-        <v>1.318696161043324</v>
+        <v>1.037473305168923</v>
       </c>
       <c r="G1765" t="n">
-        <v>3.821782052519195</v>
+        <v>3.653048338994554</v>
       </c>
     </row>
     <row r="1766">
@@ -42134,16 +42134,16 @@
         <v>3.028879780391293</v>
       </c>
       <c r="D1766" t="n">
-        <v>0.5069710756295768</v>
+        <v>0.0839214023458883</v>
       </c>
       <c r="E1766" t="n">
-        <v>3.231311786329377</v>
+        <v>3.062091917015901</v>
       </c>
       <c r="F1766" t="n">
-        <v>1.318696161043324</v>
+        <v>1.037473305168923</v>
       </c>
       <c r="G1766" t="n">
-        <v>3.820097477017289</v>
+        <v>3.651363763492648</v>
       </c>
     </row>
     <row r="1767">
@@ -42157,16 +42157,16 @@
         <v>3.033268356072139</v>
       </c>
       <c r="D1767" t="n">
-        <v>0.5072790357143013</v>
+        <v>0.08422936243061291</v>
       </c>
       <c r="E1767" t="n">
-        <v>3.235823546044112</v>
+        <v>3.066603676730637</v>
       </c>
       <c r="F1767" t="n">
-        <v>1.319877875136024</v>
+        <v>1.038655019261623</v>
       </c>
       <c r="G1767" t="n">
-        <v>3.825195081153755</v>
+        <v>3.656461367629114</v>
       </c>
     </row>
     <row r="1768">
@@ -42180,16 +42180,16 @@
         <v>3.034928653249013</v>
       </c>
       <c r="D1768" t="n">
-        <v>0.5090607980848927</v>
+        <v>0.08601112480120426</v>
       </c>
       <c r="E1768" t="n">
-        <v>3.238196548169224</v>
+        <v>3.068976678855748</v>
       </c>
       <c r="F1768" t="n">
-        <v>1.319877875136024</v>
+        <v>1.038655019261623</v>
       </c>
       <c r="G1768" t="n">
-        <v>3.82685537833063</v>
+        <v>3.658121664805989</v>
       </c>
     </row>
     <row r="1769">
@@ -42203,16 +42203,16 @@
         <v>3.049962823512704</v>
       </c>
       <c r="D1769" t="n">
-        <v>0.5049834429478013</v>
+        <v>0.08193376966411292</v>
       </c>
       <c r="E1769" t="n">
-        <v>3.251599776378078</v>
+        <v>3.082379907064602</v>
       </c>
       <c r="F1769" t="n">
-        <v>1.319877875136024</v>
+        <v>1.038655019261623</v>
       </c>
       <c r="G1769" t="n">
-        <v>3.84188954859432</v>
+        <v>3.673155835069679</v>
       </c>
     </row>
     <row r="1770">
@@ -42226,16 +42226,16 @@
         <v>3.048277258176837</v>
       </c>
       <c r="D1770" t="n">
-        <v>0.5149755238742104</v>
+        <v>0.09192585059052205</v>
       </c>
       <c r="E1770" t="n">
-        <v>3.253911043412774</v>
+        <v>3.084691174099299</v>
       </c>
       <c r="F1770" t="n">
-        <v>1.329869956062433</v>
+        <v>1.048647100188032</v>
       </c>
       <c r="G1770" t="n">
-        <v>3.846199231814298</v>
+        <v>3.677465518289658</v>
       </c>
     </row>
     <row r="1771">
@@ -42249,16 +42249,16 @@
         <v>3.051179068073428</v>
       </c>
       <c r="D1771" t="n">
-        <v>0.5144197688181726</v>
+        <v>0.09137009553448422</v>
       </c>
       <c r="E1771" t="n">
-        <v>3.25659055128695</v>
+        <v>3.087370681973475</v>
       </c>
       <c r="F1771" t="n">
-        <v>1.328262542301355</v>
+        <v>1.047039686426954</v>
       </c>
       <c r="G1771" t="n">
-        <v>3.848136593454243</v>
+        <v>3.679402879929602</v>
       </c>
     </row>
     <row r="1772">
@@ -42272,16 +42272,16 @@
         <v>3.056704057212575</v>
       </c>
       <c r="D1772" t="n">
-        <v>0.5112054164048612</v>
+        <v>0.0881557431211728</v>
       </c>
       <c r="E1772" t="n">
-        <v>3.260829799460772</v>
+        <v>3.091609930147297</v>
       </c>
       <c r="F1772" t="n">
-        <v>1.328262542301355</v>
+        <v>1.047039686426954</v>
       </c>
       <c r="G1772" t="n">
-        <v>3.85366158259339</v>
+        <v>3.684927869068749</v>
       </c>
     </row>
     <row r="1773">
@@ -42295,16 +42295,16 @@
         <v>3.057781629850306</v>
       </c>
       <c r="D1773" t="n">
-        <v>0.4941971710022517</v>
+        <v>0.07114749771856332</v>
       </c>
       <c r="E1773" t="n">
-        <v>3.25510407393746</v>
+        <v>3.085884204623985</v>
       </c>
       <c r="F1773" t="n">
-        <v>1.331261677314329</v>
+        <v>1.050038821439928</v>
       </c>
       <c r="G1773" t="n">
-        <v>3.856538636238906</v>
+        <v>3.687804922714265</v>
       </c>
     </row>
     <row r="1774">
@@ -42318,16 +42318,16 @@
         <v>3.058531492021579</v>
       </c>
       <c r="D1774" t="n">
-        <v>0.5131568934536063</v>
+        <v>0.0901072201699179</v>
       </c>
       <c r="E1774" t="n">
-        <v>3.263437825089275</v>
+        <v>3.0942179557758</v>
       </c>
       <c r="F1774" t="n">
-        <v>1.331261677314329</v>
+        <v>1.050038821439928</v>
       </c>
       <c r="G1774" t="n">
-        <v>3.857288498410179</v>
+        <v>3.688554784885538</v>
       </c>
     </row>
     <row r="1775">
@@ -42341,16 +42341,16 @@
         <v>3.05676708948516</v>
       </c>
       <c r="D1775" t="n">
-        <v>0.514391618056415</v>
+        <v>0.09134194477272667</v>
       </c>
       <c r="E1775" t="n">
-        <v>3.262167312393979</v>
+        <v>3.092947443080504</v>
       </c>
       <c r="F1775" t="n">
-        <v>1.331261677314329</v>
+        <v>1.050038821439928</v>
       </c>
       <c r="G1775" t="n">
-        <v>3.85552409587376</v>
+        <v>3.686790382349119</v>
       </c>
     </row>
     <row r="1776">
@@ -42364,16 +42364,16 @@
         <v>3.060334699322022</v>
       </c>
       <c r="D1776" t="n">
-        <v>0.5043573542327663</v>
+        <v>0.08130768094907798</v>
       </c>
       <c r="E1776" t="n">
-        <v>3.261721216701382</v>
+        <v>3.092501347387906</v>
       </c>
       <c r="F1776" t="n">
-        <v>1.331261677314329</v>
+        <v>1.050038821439928</v>
       </c>
       <c r="G1776" t="n">
-        <v>3.859091705710621</v>
+        <v>3.690357992185981</v>
       </c>
     </row>
     <row r="1777">
@@ -42387,16 +42387,16 @@
         <v>3.084316661211631</v>
       </c>
       <c r="D1777" t="n">
-        <v>0.4993183559348995</v>
+        <v>0.07626868265121123</v>
       </c>
       <c r="E1777" t="n">
-        <v>3.283687579271844</v>
+        <v>3.114467709958369</v>
       </c>
       <c r="F1777" t="n">
-        <v>1.326222679016462</v>
+        <v>1.044999823142061</v>
       </c>
       <c r="G1777" t="n">
-        <v>3.88005026862151</v>
+        <v>3.711316555096869</v>
       </c>
     </row>
     <row r="1778">
@@ -42410,16 +42410,16 @@
         <v>3.081785372698861</v>
       </c>
       <c r="D1778" t="n">
-        <v>0.5091380740954502</v>
+        <v>0.08608840081176194</v>
       </c>
       <c r="E1778" t="n">
-        <v>3.285084178023294</v>
+        <v>3.115864308709819</v>
       </c>
       <c r="F1778" t="n">
-        <v>1.33265261923315</v>
+        <v>1.051429763358749</v>
       </c>
       <c r="G1778" t="n">
-        <v>3.881376944238752</v>
+        <v>3.712643230714112</v>
       </c>
     </row>
     <row r="1779">
@@ -42433,16 +42433,16 @@
         <v>3.067033934702486</v>
       </c>
       <c r="D1779" t="n">
-        <v>0.5109397009344041</v>
+        <v>0.08789002765071585</v>
       </c>
       <c r="E1779" t="n">
-        <v>3.271053390762501</v>
+        <v>3.101833521449026</v>
       </c>
       <c r="F1779" t="n">
-        <v>1.33265261923315</v>
+        <v>1.051429763358749</v>
       </c>
       <c r="G1779" t="n">
-        <v>3.866625506242378</v>
+        <v>3.697891792717737</v>
       </c>
     </row>
     <row r="1780">
@@ -42456,16 +42456,16 @@
         <v>3.065147691018159</v>
       </c>
       <c r="D1780" t="n">
-        <v>0.5119283826785719</v>
+        <v>0.08887870939488368</v>
       </c>
       <c r="E1780" t="n">
-        <v>3.269562619775841</v>
+        <v>3.100342750462366</v>
       </c>
       <c r="F1780" t="n">
-        <v>1.33265261923315</v>
+        <v>1.051429763358749</v>
       </c>
       <c r="G1780" t="n">
-        <v>3.86473926255805</v>
+        <v>3.696005549033409</v>
       </c>
     </row>
     <row r="1781">
@@ -42479,16 +42479,16 @@
         <v>3.067121317473999</v>
       </c>
       <c r="D1781" t="n">
-        <v>0.5199247372001105</v>
+        <v>0.09687506391642225</v>
       </c>
       <c r="E1781" t="n">
-        <v>3.274734788040296</v>
+        <v>3.105514918726821</v>
       </c>
       <c r="F1781" t="n">
-        <v>1.340648973754688</v>
+        <v>1.059426117880287</v>
       </c>
       <c r="G1781" t="n">
-        <v>3.871510701726813</v>
+        <v>3.702776988202173</v>
       </c>
     </row>
     <row r="1782">
@@ -42502,16 +42502,16 @@
         <v>3.078959898064911</v>
       </c>
       <c r="D1782" t="n">
-        <v>0.5249084878720192</v>
+        <v>0.101858814588331</v>
       </c>
       <c r="E1782" t="n">
-        <v>3.288566868899971</v>
+        <v>3.119346999586496</v>
       </c>
       <c r="F1782" t="n">
-        <v>1.345632724426597</v>
+        <v>1.064409868552196</v>
       </c>
       <c r="G1782" t="n">
-        <v>3.886339532720871</v>
+        <v>3.71760581919623</v>
       </c>
     </row>
     <row r="1783">
@@ -42525,16 +42525,16 @@
         <v>3.0856881010767</v>
       </c>
       <c r="D1783" t="n">
-        <v>0.5312946268215747</v>
+        <v>0.1082449535378865</v>
       </c>
       <c r="E1783" t="n">
-        <v>3.297849527491583</v>
+        <v>3.128629658178107</v>
       </c>
       <c r="F1783" t="n">
-        <v>1.345632724426597</v>
+        <v>1.064409868552196</v>
       </c>
       <c r="G1783" t="n">
-        <v>3.89306773573266</v>
+        <v>3.724334022208019</v>
       </c>
     </row>
     <row r="1784">
@@ -42548,16 +42548,16 @@
         <v>3.089704189836242</v>
       </c>
       <c r="D1784" t="n">
-        <v>0.5194892765029421</v>
+        <v>0.09643960321925388</v>
       </c>
       <c r="E1784" t="n">
-        <v>3.297143476123672</v>
+        <v>3.127923606810197</v>
       </c>
       <c r="F1784" t="n">
-        <v>1.333827374107964</v>
+        <v>1.052604518233563</v>
       </c>
       <c r="G1784" t="n">
-        <v>3.890000614301022</v>
+        <v>3.721266900776381</v>
       </c>
     </row>
     <row r="1785">
@@ -42571,16 +42571,16 @@
         <v>3.095651647446132</v>
       </c>
       <c r="D1785" t="n">
-        <v>0.5282210872816083</v>
+        <v>0.1051714139979201</v>
       </c>
       <c r="E1785" t="n">
-        <v>3.306583658045028</v>
+        <v>3.137363788731553</v>
       </c>
       <c r="F1785" t="n">
-        <v>1.342559184886631</v>
+        <v>1.06133632901223</v>
       </c>
       <c r="G1785" t="n">
-        <v>3.901187158378112</v>
+        <v>3.732453444853471</v>
       </c>
     </row>
     <row r="1786">
@@ -42594,16 +42594,16 @@
         <v>3.090962466394117</v>
       </c>
       <c r="D1786" t="n">
-        <v>0.5345579739260603</v>
+        <v>0.1115083006423721</v>
       </c>
       <c r="E1786" t="n">
-        <v>3.304429231650794</v>
+        <v>3.135209362337319</v>
       </c>
       <c r="F1786" t="n">
-        <v>1.342559184886631</v>
+        <v>1.06133632901223</v>
       </c>
       <c r="G1786" t="n">
-        <v>3.896497977326097</v>
+        <v>3.727764263801456</v>
       </c>
     </row>
     <row r="1787">
@@ -42617,16 +42617,16 @@
         <v>3.100925124196311</v>
       </c>
       <c r="D1787" t="n">
-        <v>0.5370924216534286</v>
+        <v>0.1140427483697404</v>
       </c>
       <c r="E1787" t="n">
-        <v>3.315405668543935</v>
+        <v>3.14618579923046</v>
       </c>
       <c r="F1787" t="n">
-        <v>1.342559184886631</v>
+        <v>1.06133632901223</v>
       </c>
       <c r="G1787" t="n">
-        <v>3.906460635128291</v>
+        <v>3.73772692160365</v>
       </c>
     </row>
     <row r="1788">
@@ -42640,16 +42640,16 @@
         <v>3.09333980438922</v>
       </c>
       <c r="D1788" t="n">
-        <v>0.5370165226728241</v>
+        <v>0.1139668493891359</v>
       </c>
       <c r="E1788" t="n">
-        <v>3.307789989144603</v>
+        <v>3.138570119831128</v>
       </c>
       <c r="F1788" t="n">
-        <v>1.343322445575958</v>
+        <v>1.062099589701556</v>
       </c>
       <c r="G1788" t="n">
-        <v>3.899333271734797</v>
+        <v>3.730599558210156</v>
       </c>
     </row>
     <row r="1789">
@@ -42663,16 +42663,16 @@
         <v>3.071104380179594</v>
       </c>
       <c r="D1789" t="n">
-        <v>0.5265143331134774</v>
+        <v>0.1034646598297893</v>
       </c>
       <c r="E1789" t="n">
-        <v>3.281353689111238</v>
+        <v>3.112133819797763</v>
       </c>
       <c r="F1789" t="n">
-        <v>1.332820256016611</v>
+        <v>1.05159740014221</v>
       </c>
       <c r="G1789" t="n">
-        <v>3.870796533789562</v>
+        <v>3.702062820264921</v>
       </c>
     </row>
     <row r="1790">
@@ -42686,16 +42686,16 @@
         <v>3.071805220025715</v>
       </c>
       <c r="D1790" t="n">
-        <v>0.5246810704343611</v>
+        <v>0.1016313971506729</v>
       </c>
       <c r="E1790" t="n">
-        <v>3.281321223885713</v>
+        <v>3.112101354572238</v>
       </c>
       <c r="F1790" t="n">
-        <v>1.332820256016611</v>
+        <v>1.05159740014221</v>
       </c>
       <c r="G1790" t="n">
-        <v>3.871497373635683</v>
+        <v>3.702763660111043</v>
       </c>
     </row>
     <row r="1791">
@@ -42709,16 +42709,16 @@
         <v>3.072322299854575</v>
       </c>
       <c r="D1791" t="n">
-        <v>0.5196719553727771</v>
+        <v>0.09662228208908896</v>
       </c>
       <c r="E1791" t="n">
-        <v>3.279834657689939</v>
+        <v>3.110614788376464</v>
       </c>
       <c r="F1791" t="n">
-        <v>1.331825678458076</v>
+        <v>1.050602822583675</v>
       </c>
       <c r="G1791" t="n">
-        <v>3.871417706929422</v>
+        <v>3.702683993404781</v>
       </c>
     </row>
     <row r="1792">
@@ -42732,16 +42732,16 @@
         <v>3.07155002509494</v>
       </c>
       <c r="D1792" t="n">
-        <v>0.5159663987359625</v>
+        <v>0.09291672545227436</v>
       </c>
       <c r="E1792" t="n">
-        <v>3.277580160275579</v>
+        <v>3.108360290962103</v>
       </c>
       <c r="F1792" t="n">
-        <v>1.329956003200441</v>
+        <v>1.04873314732604</v>
       </c>
       <c r="G1792" t="n">
-        <v>3.869523627015206</v>
+        <v>3.700789913490566</v>
       </c>
     </row>
     <row r="1793">
@@ -42755,16 +42755,16 @@
         <v>3.071969877157259</v>
       </c>
       <c r="D1793" t="n">
-        <v>0.517198724093328</v>
+        <v>0.09414905080963987</v>
       </c>
       <c r="E1793" t="n">
-        <v>3.278492942480844</v>
+        <v>3.109273073167369</v>
       </c>
       <c r="F1793" t="n">
-        <v>1.330586379572479</v>
+        <v>1.049363523698078</v>
       </c>
       <c r="G1793" t="n">
-        <v>3.870321704900749</v>
+        <v>3.701587991376108</v>
       </c>
     </row>
     <row r="1794">
@@ -42778,16 +42778,16 @@
         <v>3.076099785321473</v>
       </c>
       <c r="D1794" t="n">
-        <v>0.5275267211091802</v>
+        <v>0.1044770478254921</v>
       </c>
       <c r="E1794" t="n">
-        <v>3.286754049451398</v>
+        <v>3.117534180137923</v>
       </c>
       <c r="F1794" t="n">
-        <v>1.340914376588331</v>
+        <v>1.05969152071393</v>
       </c>
       <c r="G1794" t="n">
-        <v>3.880648411274473</v>
+        <v>3.711914697749833</v>
       </c>
     </row>
     <row r="1795">
@@ -42801,16 +42801,16 @@
         <v>3.082620445523309</v>
       </c>
       <c r="D1795" t="n">
-        <v>0.5276430562567359</v>
+        <v>0.1045933829730478</v>
       </c>
       <c r="E1795" t="n">
-        <v>3.293321243712257</v>
+        <v>3.124101374398781</v>
       </c>
       <c r="F1795" t="n">
-        <v>1.341030711735887</v>
+        <v>1.059807855861486</v>
       </c>
       <c r="G1795" t="n">
-        <v>3.887238872564843</v>
+        <v>3.718505159040202</v>
       </c>
     </row>
     <row r="1796">
@@ -42824,16 +42824,16 @@
         <v>3.079594415968698</v>
       </c>
       <c r="D1796" t="n">
-        <v>0.5257976466798684</v>
+        <v>0.1027479733961802</v>
       </c>
       <c r="E1796" t="n">
-        <v>3.289557050326898</v>
+        <v>3.120337181013423</v>
       </c>
       <c r="F1796" t="n">
-        <v>1.341030711735887</v>
+        <v>1.059807855861486</v>
       </c>
       <c r="G1796" t="n">
-        <v>3.884212843010232</v>
+        <v>3.715479129485591</v>
       </c>
     </row>
     <row r="1797">
@@ -42847,16 +42847,16 @@
         <v>3.079532703829831</v>
       </c>
       <c r="D1797" t="n">
-        <v>0.5272960792049672</v>
+        <v>0.1042464059212791</v>
       </c>
       <c r="E1797" t="n">
-        <v>3.290094711198071</v>
+        <v>3.120874841884596</v>
       </c>
       <c r="F1797" t="n">
-        <v>1.342529144260986</v>
+        <v>1.061306288386585</v>
       </c>
       <c r="G1797" t="n">
-        <v>3.885050190386425</v>
+        <v>3.716316476861784</v>
       </c>
     </row>
     <row r="1798">
@@ -42870,16 +42870,16 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1798" t="n">
-        <v>0.5192318270122334</v>
+        <v>0.09618215372854527</v>
       </c>
       <c r="E1798" t="n">
-        <v>3.288146988264289</v>
+        <v>3.118927118950814</v>
       </c>
       <c r="F1798" t="n">
-        <v>1.334464892068252</v>
+        <v>1.053242036193851</v>
       </c>
       <c r="G1798" t="n">
-        <v>3.881489617014096</v>
+        <v>3.712755903489455</v>
       </c>
     </row>
     <row r="1799">
@@ -42893,16 +42893,16 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1799" t="n">
-        <v>0.517901859551021</v>
+        <v>0.09485218626733294</v>
       </c>
       <c r="E1799" t="n">
-        <v>3.287615001279804</v>
+        <v>3.118395131966329</v>
       </c>
       <c r="F1799" t="n">
-        <v>1.334464892068252</v>
+        <v>1.053242036193851</v>
       </c>
       <c r="G1799" t="n">
-        <v>3.881489617014096</v>
+        <v>3.712755903489455</v>
       </c>
     </row>
     <row r="1800">
@@ -42916,16 +42916,16 @@
         <v>3.083027154880305</v>
       </c>
       <c r="D1800" t="n">
-        <v>0.7457665422845321</v>
+        <v>0.3227168690008441</v>
       </c>
       <c r="E1800" t="n">
-        <v>3.380977347480371</v>
+        <v>3.211757478166896</v>
       </c>
       <c r="F1800" t="n">
-        <v>1.334464892068252</v>
+        <v>1.053242036193851</v>
       </c>
       <c r="G1800" t="n">
-        <v>3.883706090121258</v>
+        <v>3.714972376596617</v>
       </c>
     </row>
     <row r="1801">
@@ -42939,16 +42939,16 @@
         <v>3.090561751225397</v>
       </c>
       <c r="D1801" t="n">
-        <v>0.9938681061517489</v>
+        <v>0.5708184328680609</v>
       </c>
       <c r="E1801" t="n">
-        <v>3.48775256937235</v>
+        <v>3.318532700058875</v>
       </c>
       <c r="F1801" t="n">
-        <v>1.334464892068252</v>
+        <v>1.053242036193851</v>
       </c>
       <c r="G1801" t="n">
-        <v>3.89124068646635</v>
+        <v>3.72250697294171</v>
       </c>
     </row>
     <row r="1802">
@@ -42956,22 +42956,22 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>2.895436922045264</v>
+        <v>2.895204195910388</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
       </c>
       <c r="D1802" t="n">
-        <v>1.284679268937456</v>
+        <v>0.8676568322613912</v>
       </c>
       <c r="E1802" t="n">
-        <v>3.605500045460091</v>
+        <v>3.438691070789664</v>
       </c>
       <c r="F1802" t="n">
-        <v>1.446034519686212</v>
+        <v>1.168096524674978</v>
       </c>
       <c r="G1802" t="n">
-        <v>3.959605474010583</v>
+        <v>3.792842677003843</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231205.xlsx
+++ b/tame_output/ON/bt/strategyON_20231205.xlsx
@@ -41921,7 +41921,7 @@
         <v>45219</v>
       </c>
       <c r="B1757" t="n">
-        <v>2.902669647939156</v>
+        <v>2.902669647939157</v>
       </c>
       <c r="C1757" t="n">
         <v>2.968547780644436</v>
@@ -41944,7 +41944,7 @@
         <v>45220</v>
       </c>
       <c r="B1758" t="n">
-        <v>2.91290325494784</v>
+        <v>2.912903254947841</v>
       </c>
       <c r="C1758" t="n">
         <v>2.965146865274802</v>
@@ -42174,7 +42174,7 @@
         <v>45230</v>
       </c>
       <c r="B1768" t="n">
-        <v>3.05975199725568</v>
+        <v>3.059751997255681</v>
       </c>
       <c r="C1768" t="n">
         <v>3.034928653249013</v>
@@ -42197,7 +42197,7 @@
         <v>45231</v>
       </c>
       <c r="B1769" t="n">
-        <v>3.093259956227613</v>
+        <v>3.093259956227614</v>
       </c>
       <c r="C1769" t="n">
         <v>3.049962823512704</v>
@@ -42243,7 +42243,7 @@
         <v>45233</v>
       </c>
       <c r="B1771" t="n">
-        <v>3.069025022408316</v>
+        <v>3.069025022408317</v>
       </c>
       <c r="C1771" t="n">
         <v>3.051179068073428</v>
@@ -42266,7 +42266,7 @@
         <v>45234</v>
       </c>
       <c r="B1772" t="n">
-        <v>3.085392865708494</v>
+        <v>3.085392865708495</v>
       </c>
       <c r="C1772" t="n">
         <v>3.056704057212575</v>
@@ -42289,7 +42289,7 @@
         <v>45235</v>
       </c>
       <c r="B1773" t="n">
-        <v>3.073923642968023</v>
+        <v>3.073923642968024</v>
       </c>
       <c r="C1773" t="n">
         <v>3.057781629850306</v>
@@ -42312,7 +42312,7 @@
         <v>45236</v>
       </c>
       <c r="B1774" t="n">
-        <v>3.074518669066012</v>
+        <v>3.074518669066013</v>
       </c>
       <c r="C1774" t="n">
         <v>3.058531492021579</v>
@@ -42335,7 +42335,7 @@
         <v>45237</v>
       </c>
       <c r="B1775" t="n">
-        <v>3.087505451293021</v>
+        <v>3.087505451293022</v>
       </c>
       <c r="C1775" t="n">
         <v>3.05676708948516</v>
@@ -42358,7 +42358,7 @@
         <v>45238</v>
       </c>
       <c r="B1776" t="n">
-        <v>3.125945945239774</v>
+        <v>3.125945945239775</v>
       </c>
       <c r="C1776" t="n">
         <v>3.060334699322022</v>
@@ -42404,7 +42404,7 @@
         <v>45240</v>
       </c>
       <c r="B1778" t="n">
-        <v>3.135555340167861</v>
+        <v>3.135555340167862</v>
       </c>
       <c r="C1778" t="n">
         <v>3.081785372698861</v>
@@ -42427,7 +42427,7 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.134141625216942</v>
+        <v>3.134141625216943</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
@@ -42450,7 +42450,7 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.132018996454038</v>
+        <v>3.132018996454039</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780867</v>
+        <v>3.120443325780868</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42496,7 +42496,7 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.09520660653793</v>
+        <v>3.095206606537931</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
@@ -42519,7 +42519,7 @@
         <v>45245</v>
       </c>
       <c r="B1783" t="n">
-        <v>3.147410092597766</v>
+        <v>3.147410092597767</v>
       </c>
       <c r="C1783" t="n">
         <v>3.0856881010767</v>
@@ -42542,7 +42542,7 @@
         <v>45246</v>
       </c>
       <c r="B1784" t="n">
-        <v>3.120684616527685</v>
+        <v>3.120684616527686</v>
       </c>
       <c r="C1784" t="n">
         <v>3.089704189836242</v>
@@ -42565,7 +42565,7 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844644</v>
+        <v>3.118866618844645</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502547</v>
+        <v>3.141819250502548</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.14673011872803</v>
+        <v>3.146730118728031</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42657,7 +42657,7 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702054</v>
+        <v>3.120735995702055</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.14605337248781</v>
+        <v>3.146053372487811</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42703,7 +42703,7 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.14626574482338</v>
+        <v>3.146265744823381</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524821</v>
+        <v>3.157777201524822</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068701</v>
+        <v>3.157294380068702</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714842</v>
+        <v>3.147014107714843</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42795,7 +42795,7 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.136752015083875</v>
+        <v>3.136752015083876</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
@@ -42818,7 +42818,7 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666732</v>
+        <v>3.162269743666733</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097097</v>
+        <v>3.163432091097098</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.185514355963478</v>
+        <v>3.185514355963479</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
